--- a/domain_knowledge/spreadsheet_samples/rfs_data_template.xlsx
+++ b/domain_knowledge/spreadsheet_samples/rfs_data_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\RLC-Agent_local_copy\domain_knowledge\spreadsheet_samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\RLC-Agent\domain_knowledge\spreadsheet_samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B98A11F-BB1C-440E-A7E6-D77E73429DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F657197C-79B3-4213-8083-6661CFC9E1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="2205" windowWidth="21600" windowHeight="11835" firstSheet="3" activeTab="3" xr2:uid="{9AD7503B-AB8C-4E18-ACB5-1FDC8C829F09}"/>
+    <workbookView xWindow="6960" yWindow="1860" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{9AD7503B-AB8C-4E18-ACB5-1FDC8C829F09}"/>
   </bookViews>
   <sheets>
     <sheet name="fuel_prod_by_type" sheetId="21" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="99">
   <si>
     <t>D3 RIN Generation</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>Total D3 Production</t>
-  </si>
-  <si>
-    <t>(rins)</t>
   </si>
   <si>
     <t>D3 Fuel Production</t>
@@ -413,11 +410,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -771,70 +768,70 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" t="s">
         <v>88</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" t="s">
         <v>88</v>
       </c>
-      <c r="D3" t="s">
+      <c r="I3" t="s">
         <v>88</v>
       </c>
-      <c r="E3" t="s">
+      <c r="J3" t="s">
         <v>88</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>88</v>
       </c>
-      <c r="G3" t="s">
+      <c r="L3" t="s">
         <v>89</v>
       </c>
-      <c r="H3" t="s">
+      <c r="M3" t="s">
         <v>89</v>
       </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
         <v>89</v>
       </c>
-      <c r="J3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U3" t="s">
         <v>90</v>
-      </c>
-      <c r="M3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" t="s">
-        <v>88</v>
-      </c>
-      <c r="R3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
         <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -846,13 +843,13 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" t="s">
         <v>93</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>94</v>
-      </c>
-      <c r="J4" t="s">
-        <v>95</v>
       </c>
       <c r="K4" t="s">
         <v>10</v>
@@ -886,967 +883,967 @@
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>40179</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>40210</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>40238</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>40269</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>40299</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>40330</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>40360</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>40391</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>40422</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>40452</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>40483</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>40513</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>40544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>40575</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>40603</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>40634</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>40664</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>40695</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>40725</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>40756</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>40787</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="4">
         <v>40817</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>40848</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>40878</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>40909</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="4">
         <v>40940</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="4">
         <v>40969</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="4">
         <v>41000</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="4">
         <v>41030</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="4">
         <v>41061</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>41091</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="4">
         <v>41122</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="4">
         <v>41153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="4">
         <v>41183</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="4">
         <v>41214</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="4">
         <v>41244</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="4">
         <v>41275</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="4">
         <v>41306</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="4">
         <v>41334</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="4">
         <v>41365</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="4">
         <v>41395</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="4">
         <v>41426</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="4">
         <v>41456</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="4">
         <v>41487</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="4">
         <v>41518</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>41548</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="4">
         <v>41579</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="4">
         <v>41609</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="4">
         <v>41640</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="4">
         <v>41671</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="4">
         <v>41699</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="4">
         <v>41730</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="4">
         <v>41760</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="4">
         <v>41791</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="4">
         <v>41821</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
+      <c r="A60" s="4">
         <v>41852</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="A61" s="4">
         <v>41883</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+      <c r="A62" s="4">
         <v>41913</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="A63" s="4">
         <v>41944</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+      <c r="A64" s="4">
         <v>41974</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
+      <c r="A65" s="4">
         <v>42005</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+      <c r="A66" s="4">
         <v>42036</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
+      <c r="A67" s="4">
         <v>42064</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
+      <c r="A68" s="4">
         <v>42095</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="A69" s="4">
         <v>42125</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="A70" s="4">
         <v>42156</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+      <c r="A71" s="4">
         <v>42186</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
+      <c r="A72" s="4">
         <v>42217</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+      <c r="A73" s="4">
         <v>42248</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
+      <c r="A74" s="4">
         <v>42278</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
+      <c r="A75" s="4">
         <v>42309</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
+      <c r="A76" s="4">
         <v>42339</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+      <c r="A77" s="4">
         <v>42370</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+      <c r="A78" s="4">
         <v>42401</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+      <c r="A79" s="4">
         <v>42430</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+      <c r="A80" s="4">
         <v>42461</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="A81" s="4">
         <v>42491</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+      <c r="A82" s="4">
         <v>42522</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+      <c r="A83" s="4">
         <v>42552</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="A84" s="4">
         <v>42583</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="A85" s="4">
         <v>42614</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="A86" s="4">
         <v>42644</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="A87" s="4">
         <v>42675</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="A88" s="4">
         <v>42705</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+      <c r="A89" s="4">
         <v>42736</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+      <c r="A90" s="4">
         <v>42767</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="A91" s="4">
         <v>42795</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="A92" s="4">
         <v>42826</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="A93" s="4">
         <v>42856</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="A94" s="4">
         <v>42887</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="A95" s="4">
         <v>42917</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="A96" s="4">
         <v>42948</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="A97" s="4">
         <v>42979</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="A98" s="4">
         <v>43009</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
+      <c r="A99" s="4">
         <v>43040</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
+      <c r="A100" s="4">
         <v>43070</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
+      <c r="A101" s="4">
         <v>43101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="A102" s="4">
         <v>43132</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="A103" s="4">
         <v>43160</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="A104" s="4">
         <v>43191</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="A105" s="4">
         <v>43221</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="A106" s="4">
         <v>43252</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="A107" s="4">
         <v>43282</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="A108" s="4">
         <v>43313</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="A109" s="4">
         <v>43344</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="A110" s="4">
         <v>43374</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="A111" s="4">
         <v>43405</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="A112" s="4">
         <v>43435</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
+      <c r="A113" s="4">
         <v>43466</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
+      <c r="A114" s="4">
         <v>43497</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
+      <c r="A115" s="4">
         <v>43525</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
+      <c r="A116" s="4">
         <v>43556</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="A117" s="4">
         <v>43586</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
+      <c r="A118" s="4">
         <v>43617</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
+      <c r="A119" s="4">
         <v>43647</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
+      <c r="A120" s="4">
         <v>43678</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
+      <c r="A121" s="4">
         <v>43709</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
+      <c r="A122" s="4">
         <v>43739</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
+      <c r="A123" s="4">
         <v>43770</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="A124" s="4">
         <v>43800</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="A125" s="4">
         <v>43831</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
+      <c r="A126" s="4">
         <v>43862</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
+      <c r="A127" s="4">
         <v>43891</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
+      <c r="A128" s="4">
         <v>43922</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="A129" s="4">
         <v>43952</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
+      <c r="A130" s="4">
         <v>43983</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
+      <c r="A131" s="4">
         <v>44013</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
+      <c r="A132" s="4">
         <v>44044</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="6">
+      <c r="A133" s="4">
         <v>44075</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="6">
+      <c r="A134" s="4">
         <v>44105</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="6">
+      <c r="A135" s="4">
         <v>44136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="6">
+      <c r="A136" s="4">
         <v>44166</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
+      <c r="A137" s="4">
         <v>44197</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="6">
+      <c r="A138" s="4">
         <v>44228</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="6">
+      <c r="A139" s="4">
         <v>44256</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="6">
+      <c r="A140" s="4">
         <v>44287</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="A141" s="4">
         <v>44317</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
+      <c r="A142" s="4">
         <v>44348</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
+      <c r="A143" s="4">
         <v>44378</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="A144" s="4">
         <v>44409</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
+      <c r="A145" s="4">
         <v>44440</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="A146" s="4">
         <v>44470</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
+      <c r="A147" s="4">
         <v>44501</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
+      <c r="A148" s="4">
         <v>44531</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
+      <c r="A149" s="4">
         <v>44562</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
+      <c r="A150" s="4">
         <v>44593</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
+      <c r="A151" s="4">
         <v>44621</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
+      <c r="A152" s="4">
         <v>44652</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
+      <c r="A153" s="4">
         <v>44682</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="6">
+      <c r="A154" s="4">
         <v>44713</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
+      <c r="A155" s="4">
         <v>44743</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
+      <c r="A156" s="4">
         <v>44774</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
+      <c r="A157" s="4">
         <v>44805</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
+      <c r="A158" s="4">
         <v>44835</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
+      <c r="A159" s="4">
         <v>44866</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
+      <c r="A160" s="4">
         <v>44896</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
+      <c r="A161" s="4">
         <v>44927</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="6">
+      <c r="A162" s="4">
         <v>44958</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="6">
+      <c r="A163" s="4">
         <v>44986</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
+      <c r="A164" s="4">
         <v>45017</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="6">
+      <c r="A165" s="4">
         <v>45047</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="6">
+      <c r="A166" s="4">
         <v>45078</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="6">
+      <c r="A167" s="4">
         <v>45108</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="6">
+      <c r="A168" s="4">
         <v>45139</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
+      <c r="A169" s="4">
         <v>45170</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="6">
+      <c r="A170" s="4">
         <v>45200</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="6">
+      <c r="A171" s="4">
         <v>45231</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="6">
+      <c r="A172" s="4">
         <v>45261</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="6">
+      <c r="A173" s="4">
         <v>45292</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="6">
+      <c r="A174" s="4">
         <v>45323</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="6">
+      <c r="A175" s="4">
         <v>45352</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
+      <c r="A176" s="4">
         <v>45383</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
+      <c r="A177" s="4">
         <v>45413</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="6">
+      <c r="A178" s="4">
         <v>45444</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
+      <c r="A179" s="4">
         <v>45474</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="6">
+      <c r="A180" s="4">
         <v>45505</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="6">
+      <c r="A181" s="4">
         <v>45536</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
+      <c r="A182" s="4">
         <v>45566</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+      <c r="A183" s="4">
         <v>45597</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
+      <c r="A184" s="4">
         <v>45627</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
+      <c r="A185" s="4">
         <v>45658</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="6">
+      <c r="A186" s="4">
         <v>45689</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="6">
+      <c r="A187" s="4">
         <v>45717</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="6">
+      <c r="A188" s="4">
         <v>45748</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="6">
+      <c r="A189" s="4">
         <v>45778</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="6">
+      <c r="A190" s="4">
         <v>45809</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="6">
+      <c r="A191" s="4">
         <v>45839</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="6">
+      <c r="A192" s="4">
         <v>45870</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="6">
+      <c r="A193" s="4">
         <v>45901</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="6">
+      <c r="A194" s="4">
         <v>45931</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="6">
+      <c r="A195" s="4">
         <v>45962</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="6">
+      <c r="A196" s="4">
         <v>45992</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="6">
+      <c r="A197" s="4">
         <v>46023</v>
       </c>
     </row>
@@ -1867,70 +1864,70 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" t="s">
         <v>88</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" t="s">
         <v>88</v>
       </c>
-      <c r="D3" t="s">
+      <c r="I3" t="s">
         <v>88</v>
       </c>
-      <c r="E3" t="s">
+      <c r="J3" t="s">
         <v>88</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>88</v>
       </c>
-      <c r="G3" t="s">
+      <c r="L3" t="s">
         <v>89</v>
       </c>
-      <c r="H3" t="s">
+      <c r="M3" t="s">
         <v>89</v>
       </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
         <v>89</v>
       </c>
-      <c r="J3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U3" t="s">
         <v>90</v>
-      </c>
-      <c r="M3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" t="s">
-        <v>88</v>
-      </c>
-      <c r="R3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
         <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1942,13 +1939,13 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" t="s">
         <v>93</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>94</v>
-      </c>
-      <c r="J4" t="s">
-        <v>95</v>
       </c>
       <c r="K4" t="s">
         <v>10</v>
@@ -1982,967 +1979,967 @@
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>40179</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>40210</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>40238</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>40269</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>40299</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>40330</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>40360</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>40391</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>40422</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>40452</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>40483</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>40513</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>40544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>40575</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>40603</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>40634</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>40664</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>40695</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>40725</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>40756</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>40787</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="4">
         <v>40817</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>40848</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>40878</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>40909</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="4">
         <v>40940</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="4">
         <v>40969</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="4">
         <v>41000</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="4">
         <v>41030</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="4">
         <v>41061</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>41091</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="4">
         <v>41122</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="4">
         <v>41153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="4">
         <v>41183</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="4">
         <v>41214</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="4">
         <v>41244</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="4">
         <v>41275</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="4">
         <v>41306</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="4">
         <v>41334</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="4">
         <v>41365</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="4">
         <v>41395</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="4">
         <v>41426</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="4">
         <v>41456</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="4">
         <v>41487</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="4">
         <v>41518</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>41548</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="4">
         <v>41579</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="4">
         <v>41609</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="4">
         <v>41640</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="4">
         <v>41671</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="4">
         <v>41699</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="4">
         <v>41730</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="4">
         <v>41760</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="4">
         <v>41791</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="4">
         <v>41821</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
+      <c r="A60" s="4">
         <v>41852</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="A61" s="4">
         <v>41883</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+      <c r="A62" s="4">
         <v>41913</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="A63" s="4">
         <v>41944</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+      <c r="A64" s="4">
         <v>41974</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
+      <c r="A65" s="4">
         <v>42005</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+      <c r="A66" s="4">
         <v>42036</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
+      <c r="A67" s="4">
         <v>42064</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
+      <c r="A68" s="4">
         <v>42095</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="A69" s="4">
         <v>42125</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="A70" s="4">
         <v>42156</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+      <c r="A71" s="4">
         <v>42186</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
+      <c r="A72" s="4">
         <v>42217</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+      <c r="A73" s="4">
         <v>42248</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
+      <c r="A74" s="4">
         <v>42278</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
+      <c r="A75" s="4">
         <v>42309</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
+      <c r="A76" s="4">
         <v>42339</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+      <c r="A77" s="4">
         <v>42370</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+      <c r="A78" s="4">
         <v>42401</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+      <c r="A79" s="4">
         <v>42430</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+      <c r="A80" s="4">
         <v>42461</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="A81" s="4">
         <v>42491</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+      <c r="A82" s="4">
         <v>42522</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+      <c r="A83" s="4">
         <v>42552</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="A84" s="4">
         <v>42583</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="A85" s="4">
         <v>42614</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="A86" s="4">
         <v>42644</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="A87" s="4">
         <v>42675</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="A88" s="4">
         <v>42705</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+      <c r="A89" s="4">
         <v>42736</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+      <c r="A90" s="4">
         <v>42767</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="A91" s="4">
         <v>42795</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="A92" s="4">
         <v>42826</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="A93" s="4">
         <v>42856</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="A94" s="4">
         <v>42887</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="A95" s="4">
         <v>42917</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="A96" s="4">
         <v>42948</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="A97" s="4">
         <v>42979</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="A98" s="4">
         <v>43009</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
+      <c r="A99" s="4">
         <v>43040</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
+      <c r="A100" s="4">
         <v>43070</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
+      <c r="A101" s="4">
         <v>43101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="A102" s="4">
         <v>43132</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="A103" s="4">
         <v>43160</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="A104" s="4">
         <v>43191</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="A105" s="4">
         <v>43221</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="A106" s="4">
         <v>43252</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="A107" s="4">
         <v>43282</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="A108" s="4">
         <v>43313</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="A109" s="4">
         <v>43344</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="A110" s="4">
         <v>43374</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="A111" s="4">
         <v>43405</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="A112" s="4">
         <v>43435</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
+      <c r="A113" s="4">
         <v>43466</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
+      <c r="A114" s="4">
         <v>43497</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
+      <c r="A115" s="4">
         <v>43525</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
+      <c r="A116" s="4">
         <v>43556</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="A117" s="4">
         <v>43586</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
+      <c r="A118" s="4">
         <v>43617</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
+      <c r="A119" s="4">
         <v>43647</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
+      <c r="A120" s="4">
         <v>43678</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
+      <c r="A121" s="4">
         <v>43709</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
+      <c r="A122" s="4">
         <v>43739</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
+      <c r="A123" s="4">
         <v>43770</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="A124" s="4">
         <v>43800</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="A125" s="4">
         <v>43831</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
+      <c r="A126" s="4">
         <v>43862</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
+      <c r="A127" s="4">
         <v>43891</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
+      <c r="A128" s="4">
         <v>43922</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="A129" s="4">
         <v>43952</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
+      <c r="A130" s="4">
         <v>43983</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
+      <c r="A131" s="4">
         <v>44013</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
+      <c r="A132" s="4">
         <v>44044</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="6">
+      <c r="A133" s="4">
         <v>44075</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="6">
+      <c r="A134" s="4">
         <v>44105</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="6">
+      <c r="A135" s="4">
         <v>44136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="6">
+      <c r="A136" s="4">
         <v>44166</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
+      <c r="A137" s="4">
         <v>44197</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="6">
+      <c r="A138" s="4">
         <v>44228</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="6">
+      <c r="A139" s="4">
         <v>44256</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="6">
+      <c r="A140" s="4">
         <v>44287</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="A141" s="4">
         <v>44317</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
+      <c r="A142" s="4">
         <v>44348</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
+      <c r="A143" s="4">
         <v>44378</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="A144" s="4">
         <v>44409</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
+      <c r="A145" s="4">
         <v>44440</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="A146" s="4">
         <v>44470</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
+      <c r="A147" s="4">
         <v>44501</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
+      <c r="A148" s="4">
         <v>44531</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
+      <c r="A149" s="4">
         <v>44562</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
+      <c r="A150" s="4">
         <v>44593</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
+      <c r="A151" s="4">
         <v>44621</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
+      <c r="A152" s="4">
         <v>44652</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
+      <c r="A153" s="4">
         <v>44682</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="6">
+      <c r="A154" s="4">
         <v>44713</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
+      <c r="A155" s="4">
         <v>44743</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
+      <c r="A156" s="4">
         <v>44774</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
+      <c r="A157" s="4">
         <v>44805</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
+      <c r="A158" s="4">
         <v>44835</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
+      <c r="A159" s="4">
         <v>44866</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
+      <c r="A160" s="4">
         <v>44896</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
+      <c r="A161" s="4">
         <v>44927</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="6">
+      <c r="A162" s="4">
         <v>44958</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="6">
+      <c r="A163" s="4">
         <v>44986</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
+      <c r="A164" s="4">
         <v>45017</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="6">
+      <c r="A165" s="4">
         <v>45047</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="6">
+      <c r="A166" s="4">
         <v>45078</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="6">
+      <c r="A167" s="4">
         <v>45108</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="6">
+      <c r="A168" s="4">
         <v>45139</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
+      <c r="A169" s="4">
         <v>45170</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="6">
+      <c r="A170" s="4">
         <v>45200</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="6">
+      <c r="A171" s="4">
         <v>45231</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="6">
+      <c r="A172" s="4">
         <v>45261</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="6">
+      <c r="A173" s="4">
         <v>45292</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="6">
+      <c r="A174" s="4">
         <v>45323</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="6">
+      <c r="A175" s="4">
         <v>45352</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
+      <c r="A176" s="4">
         <v>45383</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
+      <c r="A177" s="4">
         <v>45413</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="6">
+      <c r="A178" s="4">
         <v>45444</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
+      <c r="A179" s="4">
         <v>45474</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="6">
+      <c r="A180" s="4">
         <v>45505</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="6">
+      <c r="A181" s="4">
         <v>45536</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
+      <c r="A182" s="4">
         <v>45566</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+      <c r="A183" s="4">
         <v>45597</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
+      <c r="A184" s="4">
         <v>45627</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
+      <c r="A185" s="4">
         <v>45658</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="6">
+      <c r="A186" s="4">
         <v>45689</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="6">
+      <c r="A187" s="4">
         <v>45717</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="6">
+      <c r="A188" s="4">
         <v>45748</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="6">
+      <c r="A189" s="4">
         <v>45778</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="6">
+      <c r="A190" s="4">
         <v>45809</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="6">
+      <c r="A191" s="4">
         <v>45839</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="6">
+      <c r="A192" s="4">
         <v>45870</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="6">
+      <c r="A193" s="4">
         <v>45901</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="6">
+      <c r="A194" s="4">
         <v>45931</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="6">
+      <c r="A195" s="4">
         <v>45962</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="6">
+      <c r="A196" s="4">
         <v>45992</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="6">
+      <c r="A197" s="4">
         <v>46023</v>
       </c>
     </row>
@@ -3174,105 +3171,105 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4" t="s">
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4" t="s">
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4" t="s">
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
       <c r="AC3" s="2" t="s">
         <v>7</v>
       </c>
@@ -4326,11 +4323,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="Z3:AB3"/>
-    <mergeCell ref="B2:P2"/>
     <mergeCell ref="Q2:AC2"/>
-    <mergeCell ref="Q3:S3"/>
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="W3:Y3"/>
   </mergeCells>
@@ -4374,106 +4369,88 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4" t="s">
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4" t="s">
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4" t="s">
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
       <c r="AC3" s="2" t="s">
         <v>7</v>
       </c>
@@ -5550,110 +5527,86 @@
     </row>
     <row r="2" spans="1:57" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="X2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
     </row>
     <row r="3" spans="1:57" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
-      <c r="B3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="Q3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="R3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="S3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="T3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
+      <c r="U3" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
@@ -5670,13 +5623,13 @@
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -5685,28 +5638,28 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" t="s">
         <v>61</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>62</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" t="s">
         <v>63</v>
       </c>
-      <c r="I4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>64</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>65</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>66</v>
-      </c>
-      <c r="M4" t="s">
-        <v>67</v>
       </c>
       <c r="N4" t="s">
         <v>9</v>
@@ -5715,254 +5668,254 @@
         <v>10</v>
       </c>
       <c r="P4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>59</v>
       </c>
-      <c r="R4" t="s">
-        <v>60</v>
-      </c>
       <c r="S4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T4" t="s">
         <v>10</v>
       </c>
       <c r="U4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V4" t="s">
+        <v>34</v>
+      </c>
+      <c r="W4" t="s">
         <v>35</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>36</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>37</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>38</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>39</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>40</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>41</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>42</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>43</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>44</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>45</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>46</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>48</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>49</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>50</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>51</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>52</v>
       </c>
-      <c r="AN4" t="s">
-        <v>53</v>
-      </c>
       <c r="AO4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP4" t="s">
         <v>22</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>23</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>24</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>25</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>26</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>27</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>28</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>29</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>30</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>31</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>32</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>33</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>34</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>35</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>36</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>37</v>
       </c>
-      <c r="BE4" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>40179</v>
       </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>40210</v>
       </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>40238</v>
       </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>40269</v>
       </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>40299</v>
       </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>40330</v>
       </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>40360</v>
       </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>40391</v>
       </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>40422</v>
       </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>40452</v>
       </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>40483</v>
       </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>40513</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>40544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>40575</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>40603</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>40634</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>40664</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>40695</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>40725</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>40756</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>40787</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="4">
         <v>40817</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>40848</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>40878</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>40909</v>
       </c>
     </row>
@@ -5987,110 +5940,86 @@
     </row>
     <row r="2" spans="1:57" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
     </row>
     <row r="3" spans="1:57" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
-      <c r="B3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="Q3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="R3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="S3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="T3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
+      <c r="U3" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
@@ -6107,13 +6036,13 @@
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -6122,28 +6051,28 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" t="s">
         <v>61</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>62</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" t="s">
         <v>63</v>
       </c>
-      <c r="I4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>64</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>65</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>66</v>
-      </c>
-      <c r="M4" t="s">
-        <v>67</v>
       </c>
       <c r="N4" t="s">
         <v>9</v>
@@ -6152,254 +6081,254 @@
         <v>10</v>
       </c>
       <c r="P4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>59</v>
       </c>
-      <c r="R4" t="s">
-        <v>60</v>
-      </c>
       <c r="S4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T4" t="s">
         <v>10</v>
       </c>
       <c r="U4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V4" t="s">
+        <v>34</v>
+      </c>
+      <c r="W4" t="s">
         <v>35</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>36</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>37</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>38</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>39</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>40</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>41</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>42</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>43</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>44</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>45</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>46</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>48</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>49</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>50</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>51</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>52</v>
       </c>
-      <c r="AN4" t="s">
-        <v>53</v>
-      </c>
       <c r="AO4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP4" t="s">
         <v>22</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>23</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>24</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>25</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>26</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>27</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>28</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>29</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>30</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>31</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>32</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>33</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>34</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>35</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>36</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>37</v>
       </c>
-      <c r="BE4" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>40179</v>
       </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>40210</v>
       </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>40238</v>
       </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>40269</v>
       </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>40299</v>
       </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>40330</v>
       </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>40360</v>
       </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>40391</v>
       </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>40422</v>
       </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>40452</v>
       </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>40483</v>
       </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>40513</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>40544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>40575</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>40603</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>40634</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>40664</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>40695</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>40725</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>40756</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>40787</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="4">
         <v>40817</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>40848</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>40878</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>40909</v>
       </c>
     </row>
@@ -6423,66 +6352,66 @@
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" t="s">
         <v>71</v>
       </c>
-      <c r="C3" t="s">
+      <c r="N3" t="s">
         <v>71</v>
       </c>
-      <c r="D3" t="s">
+      <c r="O3" t="s">
         <v>71</v>
       </c>
-      <c r="E3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" t="s">
-        <v>69</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="P3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>75</v>
+      </c>
+      <c r="R3" t="s">
+        <v>75</v>
+      </c>
+      <c r="S3" t="s">
         <v>72</v>
       </c>
-      <c r="N3" t="s">
+      <c r="T3" t="s">
         <v>72</v>
-      </c>
-      <c r="O3" t="s">
-        <v>72</v>
-      </c>
-      <c r="P3" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R3" t="s">
-        <v>76</v>
-      </c>
-      <c r="S3" t="s">
-        <v>73</v>
-      </c>
-      <c r="T3" t="s">
-        <v>73</v>
       </c>
       <c r="U3" t="s">
         <v>4</v>
@@ -6494,46 +6423,46 @@
         <v>4</v>
       </c>
       <c r="X3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" t="s">
         <v>74</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AB3" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AC3" t="s">
         <v>74</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AD3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP3" t="s">
         <v>75</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>76</v>
       </c>
       <c r="AS3" t="s">
         <v>4</v>
       </c>
       <c r="AV3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AY3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.25">
@@ -6547,13 +6476,13 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
@@ -6580,10 +6509,10 @@
         <v>10</v>
       </c>
       <c r="P4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R4" t="s">
         <v>10</v>
@@ -6686,967 +6615,967 @@
       </c>
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>40179</v>
       </c>
     </row>
     <row r="6" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>40210</v>
       </c>
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>40238</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>40269</v>
       </c>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>40299</v>
       </c>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>40330</v>
       </c>
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>40360</v>
       </c>
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>40391</v>
       </c>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>40422</v>
       </c>
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>40452</v>
       </c>
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>40483</v>
       </c>
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>40513</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>40544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>40575</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>40603</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>40634</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>40664</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>40695</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>40725</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>40756</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>40787</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="4">
         <v>40817</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>40848</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>40878</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>40909</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="4">
         <v>40940</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="4">
         <v>40969</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="4">
         <v>41000</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="4">
         <v>41030</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="4">
         <v>41061</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>41091</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="4">
         <v>41122</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="4">
         <v>41153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="4">
         <v>41183</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="4">
         <v>41214</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="4">
         <v>41244</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="4">
         <v>41275</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="4">
         <v>41306</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="4">
         <v>41334</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="4">
         <v>41365</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="4">
         <v>41395</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="4">
         <v>41426</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="4">
         <v>41456</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="4">
         <v>41487</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="4">
         <v>41518</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>41548</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="4">
         <v>41579</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="4">
         <v>41609</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="4">
         <v>41640</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="4">
         <v>41671</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="4">
         <v>41699</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="4">
         <v>41730</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="4">
         <v>41760</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="4">
         <v>41791</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="4">
         <v>41821</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
+      <c r="A60" s="4">
         <v>41852</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="A61" s="4">
         <v>41883</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+      <c r="A62" s="4">
         <v>41913</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="A63" s="4">
         <v>41944</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+      <c r="A64" s="4">
         <v>41974</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
+      <c r="A65" s="4">
         <v>42005</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+      <c r="A66" s="4">
         <v>42036</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
+      <c r="A67" s="4">
         <v>42064</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
+      <c r="A68" s="4">
         <v>42095</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="A69" s="4">
         <v>42125</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="A70" s="4">
         <v>42156</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+      <c r="A71" s="4">
         <v>42186</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
+      <c r="A72" s="4">
         <v>42217</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+      <c r="A73" s="4">
         <v>42248</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
+      <c r="A74" s="4">
         <v>42278</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
+      <c r="A75" s="4">
         <v>42309</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
+      <c r="A76" s="4">
         <v>42339</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+      <c r="A77" s="4">
         <v>42370</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+      <c r="A78" s="4">
         <v>42401</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+      <c r="A79" s="4">
         <v>42430</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+      <c r="A80" s="4">
         <v>42461</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="A81" s="4">
         <v>42491</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+      <c r="A82" s="4">
         <v>42522</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+      <c r="A83" s="4">
         <v>42552</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="A84" s="4">
         <v>42583</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="A85" s="4">
         <v>42614</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="A86" s="4">
         <v>42644</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="A87" s="4">
         <v>42675</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="A88" s="4">
         <v>42705</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+      <c r="A89" s="4">
         <v>42736</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+      <c r="A90" s="4">
         <v>42767</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="A91" s="4">
         <v>42795</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="A92" s="4">
         <v>42826</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="A93" s="4">
         <v>42856</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="A94" s="4">
         <v>42887</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="A95" s="4">
         <v>42917</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="A96" s="4">
         <v>42948</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="A97" s="4">
         <v>42979</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="A98" s="4">
         <v>43009</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
+      <c r="A99" s="4">
         <v>43040</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
+      <c r="A100" s="4">
         <v>43070</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
+      <c r="A101" s="4">
         <v>43101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="A102" s="4">
         <v>43132</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="A103" s="4">
         <v>43160</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="A104" s="4">
         <v>43191</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="A105" s="4">
         <v>43221</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="A106" s="4">
         <v>43252</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="A107" s="4">
         <v>43282</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="A108" s="4">
         <v>43313</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="A109" s="4">
         <v>43344</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="A110" s="4">
         <v>43374</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="A111" s="4">
         <v>43405</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="A112" s="4">
         <v>43435</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
+      <c r="A113" s="4">
         <v>43466</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
+      <c r="A114" s="4">
         <v>43497</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
+      <c r="A115" s="4">
         <v>43525</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
+      <c r="A116" s="4">
         <v>43556</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="A117" s="4">
         <v>43586</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
+      <c r="A118" s="4">
         <v>43617</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
+      <c r="A119" s="4">
         <v>43647</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
+      <c r="A120" s="4">
         <v>43678</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
+      <c r="A121" s="4">
         <v>43709</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
+      <c r="A122" s="4">
         <v>43739</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
+      <c r="A123" s="4">
         <v>43770</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="A124" s="4">
         <v>43800</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="A125" s="4">
         <v>43831</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
+      <c r="A126" s="4">
         <v>43862</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
+      <c r="A127" s="4">
         <v>43891</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
+      <c r="A128" s="4">
         <v>43922</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="A129" s="4">
         <v>43952</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
+      <c r="A130" s="4">
         <v>43983</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
+      <c r="A131" s="4">
         <v>44013</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
+      <c r="A132" s="4">
         <v>44044</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="6">
+      <c r="A133" s="4">
         <v>44075</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="6">
+      <c r="A134" s="4">
         <v>44105</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="6">
+      <c r="A135" s="4">
         <v>44136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="6">
+      <c r="A136" s="4">
         <v>44166</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
+      <c r="A137" s="4">
         <v>44197</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="6">
+      <c r="A138" s="4">
         <v>44228</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="6">
+      <c r="A139" s="4">
         <v>44256</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="6">
+      <c r="A140" s="4">
         <v>44287</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="A141" s="4">
         <v>44317</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
+      <c r="A142" s="4">
         <v>44348</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
+      <c r="A143" s="4">
         <v>44378</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="A144" s="4">
         <v>44409</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
+      <c r="A145" s="4">
         <v>44440</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="A146" s="4">
         <v>44470</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
+      <c r="A147" s="4">
         <v>44501</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
+      <c r="A148" s="4">
         <v>44531</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
+      <c r="A149" s="4">
         <v>44562</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
+      <c r="A150" s="4">
         <v>44593</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
+      <c r="A151" s="4">
         <v>44621</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
+      <c r="A152" s="4">
         <v>44652</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
+      <c r="A153" s="4">
         <v>44682</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="6">
+      <c r="A154" s="4">
         <v>44713</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
+      <c r="A155" s="4">
         <v>44743</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
+      <c r="A156" s="4">
         <v>44774</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
+      <c r="A157" s="4">
         <v>44805</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
+      <c r="A158" s="4">
         <v>44835</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
+      <c r="A159" s="4">
         <v>44866</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
+      <c r="A160" s="4">
         <v>44896</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
+      <c r="A161" s="4">
         <v>44927</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="6">
+      <c r="A162" s="4">
         <v>44958</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="6">
+      <c r="A163" s="4">
         <v>44986</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
+      <c r="A164" s="4">
         <v>45017</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="6">
+      <c r="A165" s="4">
         <v>45047</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="6">
+      <c r="A166" s="4">
         <v>45078</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="6">
+      <c r="A167" s="4">
         <v>45108</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="6">
+      <c r="A168" s="4">
         <v>45139</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
+      <c r="A169" s="4">
         <v>45170</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="6">
+      <c r="A170" s="4">
         <v>45200</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="6">
+      <c r="A171" s="4">
         <v>45231</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="6">
+      <c r="A172" s="4">
         <v>45261</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="6">
+      <c r="A173" s="4">
         <v>45292</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="6">
+      <c r="A174" s="4">
         <v>45323</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="6">
+      <c r="A175" s="4">
         <v>45352</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
+      <c r="A176" s="4">
         <v>45383</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
+      <c r="A177" s="4">
         <v>45413</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="6">
+      <c r="A178" s="4">
         <v>45444</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
+      <c r="A179" s="4">
         <v>45474</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="6">
+      <c r="A180" s="4">
         <v>45505</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="6">
+      <c r="A181" s="4">
         <v>45536</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
+      <c r="A182" s="4">
         <v>45566</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+      <c r="A183" s="4">
         <v>45597</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
+      <c r="A184" s="4">
         <v>45627</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
+      <c r="A185" s="4">
         <v>45658</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="6">
+      <c r="A186" s="4">
         <v>45689</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="6">
+      <c r="A187" s="4">
         <v>45717</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="6">
+      <c r="A188" s="4">
         <v>45748</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="6">
+      <c r="A189" s="4">
         <v>45778</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="6">
+      <c r="A190" s="4">
         <v>45809</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="6">
+      <c r="A191" s="4">
         <v>45839</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="6">
+      <c r="A192" s="4">
         <v>45870</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="6">
+      <c r="A193" s="4">
         <v>45901</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="6">
+      <c r="A194" s="4">
         <v>45931</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="6">
+      <c r="A195" s="4">
         <v>45962</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="6">
+      <c r="A196" s="4">
         <v>45992</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="6">
+      <c r="A197" s="4">
         <v>46023</v>
       </c>
     </row>
@@ -7667,66 +7596,66 @@
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" t="s">
         <v>71</v>
       </c>
-      <c r="C3" t="s">
+      <c r="N3" t="s">
         <v>71</v>
       </c>
-      <c r="D3" t="s">
+      <c r="O3" t="s">
         <v>71</v>
       </c>
-      <c r="E3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" t="s">
-        <v>69</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="P3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>75</v>
+      </c>
+      <c r="R3" t="s">
+        <v>75</v>
+      </c>
+      <c r="S3" t="s">
         <v>72</v>
       </c>
-      <c r="N3" t="s">
+      <c r="T3" t="s">
         <v>72</v>
-      </c>
-      <c r="O3" t="s">
-        <v>72</v>
-      </c>
-      <c r="P3" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R3" t="s">
-        <v>76</v>
-      </c>
-      <c r="S3" t="s">
-        <v>73</v>
-      </c>
-      <c r="T3" t="s">
-        <v>73</v>
       </c>
       <c r="U3" t="s">
         <v>4</v>
@@ -7738,46 +7667,46 @@
         <v>4</v>
       </c>
       <c r="X3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" t="s">
         <v>74</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AB3" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AC3" t="s">
         <v>74</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AD3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP3" t="s">
         <v>75</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>76</v>
       </c>
       <c r="AS3" t="s">
         <v>4</v>
       </c>
       <c r="AV3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AY3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.25">
@@ -7791,13 +7720,13 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
@@ -7824,10 +7753,10 @@
         <v>10</v>
       </c>
       <c r="P4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R4" t="s">
         <v>10</v>
@@ -7930,967 +7859,967 @@
       </c>
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>40179</v>
       </c>
     </row>
     <row r="6" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>40210</v>
       </c>
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>40238</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>40269</v>
       </c>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>40299</v>
       </c>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>40330</v>
       </c>
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>40360</v>
       </c>
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>40391</v>
       </c>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>40422</v>
       </c>
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>40452</v>
       </c>
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>40483</v>
       </c>
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>40513</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>40544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>40575</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>40603</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>40634</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>40664</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>40695</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>40725</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>40756</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>40787</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="4">
         <v>40817</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>40848</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>40878</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>40909</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="4">
         <v>40940</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="4">
         <v>40969</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="4">
         <v>41000</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="4">
         <v>41030</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="4">
         <v>41061</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>41091</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="4">
         <v>41122</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="4">
         <v>41153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="4">
         <v>41183</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="4">
         <v>41214</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="4">
         <v>41244</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="4">
         <v>41275</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="4">
         <v>41306</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="4">
         <v>41334</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="4">
         <v>41365</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="4">
         <v>41395</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="4">
         <v>41426</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="4">
         <v>41456</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="4">
         <v>41487</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="4">
         <v>41518</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>41548</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="4">
         <v>41579</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="4">
         <v>41609</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="4">
         <v>41640</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="4">
         <v>41671</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="4">
         <v>41699</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="4">
         <v>41730</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="4">
         <v>41760</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="4">
         <v>41791</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="4">
         <v>41821</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
+      <c r="A60" s="4">
         <v>41852</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="A61" s="4">
         <v>41883</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+      <c r="A62" s="4">
         <v>41913</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="A63" s="4">
         <v>41944</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+      <c r="A64" s="4">
         <v>41974</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
+      <c r="A65" s="4">
         <v>42005</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+      <c r="A66" s="4">
         <v>42036</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
+      <c r="A67" s="4">
         <v>42064</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
+      <c r="A68" s="4">
         <v>42095</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="A69" s="4">
         <v>42125</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="A70" s="4">
         <v>42156</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+      <c r="A71" s="4">
         <v>42186</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
+      <c r="A72" s="4">
         <v>42217</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+      <c r="A73" s="4">
         <v>42248</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
+      <c r="A74" s="4">
         <v>42278</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
+      <c r="A75" s="4">
         <v>42309</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
+      <c r="A76" s="4">
         <v>42339</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+      <c r="A77" s="4">
         <v>42370</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+      <c r="A78" s="4">
         <v>42401</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+      <c r="A79" s="4">
         <v>42430</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+      <c r="A80" s="4">
         <v>42461</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="A81" s="4">
         <v>42491</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+      <c r="A82" s="4">
         <v>42522</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+      <c r="A83" s="4">
         <v>42552</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="A84" s="4">
         <v>42583</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="A85" s="4">
         <v>42614</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="A86" s="4">
         <v>42644</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="A87" s="4">
         <v>42675</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="A88" s="4">
         <v>42705</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+      <c r="A89" s="4">
         <v>42736</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+      <c r="A90" s="4">
         <v>42767</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="A91" s="4">
         <v>42795</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="A92" s="4">
         <v>42826</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="A93" s="4">
         <v>42856</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="A94" s="4">
         <v>42887</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="A95" s="4">
         <v>42917</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="A96" s="4">
         <v>42948</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="A97" s="4">
         <v>42979</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="A98" s="4">
         <v>43009</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
+      <c r="A99" s="4">
         <v>43040</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
+      <c r="A100" s="4">
         <v>43070</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
+      <c r="A101" s="4">
         <v>43101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="A102" s="4">
         <v>43132</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="A103" s="4">
         <v>43160</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="A104" s="4">
         <v>43191</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="A105" s="4">
         <v>43221</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="A106" s="4">
         <v>43252</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="A107" s="4">
         <v>43282</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="A108" s="4">
         <v>43313</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="A109" s="4">
         <v>43344</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="A110" s="4">
         <v>43374</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="A111" s="4">
         <v>43405</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="A112" s="4">
         <v>43435</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
+      <c r="A113" s="4">
         <v>43466</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
+      <c r="A114" s="4">
         <v>43497</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
+      <c r="A115" s="4">
         <v>43525</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
+      <c r="A116" s="4">
         <v>43556</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="A117" s="4">
         <v>43586</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
+      <c r="A118" s="4">
         <v>43617</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
+      <c r="A119" s="4">
         <v>43647</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
+      <c r="A120" s="4">
         <v>43678</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
+      <c r="A121" s="4">
         <v>43709</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
+      <c r="A122" s="4">
         <v>43739</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
+      <c r="A123" s="4">
         <v>43770</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="A124" s="4">
         <v>43800</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="A125" s="4">
         <v>43831</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
+      <c r="A126" s="4">
         <v>43862</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
+      <c r="A127" s="4">
         <v>43891</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
+      <c r="A128" s="4">
         <v>43922</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="A129" s="4">
         <v>43952</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
+      <c r="A130" s="4">
         <v>43983</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
+      <c r="A131" s="4">
         <v>44013</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
+      <c r="A132" s="4">
         <v>44044</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="6">
+      <c r="A133" s="4">
         <v>44075</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="6">
+      <c r="A134" s="4">
         <v>44105</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="6">
+      <c r="A135" s="4">
         <v>44136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="6">
+      <c r="A136" s="4">
         <v>44166</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
+      <c r="A137" s="4">
         <v>44197</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="6">
+      <c r="A138" s="4">
         <v>44228</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="6">
+      <c r="A139" s="4">
         <v>44256</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="6">
+      <c r="A140" s="4">
         <v>44287</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="A141" s="4">
         <v>44317</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
+      <c r="A142" s="4">
         <v>44348</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
+      <c r="A143" s="4">
         <v>44378</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="A144" s="4">
         <v>44409</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
+      <c r="A145" s="4">
         <v>44440</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="A146" s="4">
         <v>44470</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
+      <c r="A147" s="4">
         <v>44501</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
+      <c r="A148" s="4">
         <v>44531</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
+      <c r="A149" s="4">
         <v>44562</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
+      <c r="A150" s="4">
         <v>44593</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
+      <c r="A151" s="4">
         <v>44621</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
+      <c r="A152" s="4">
         <v>44652</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
+      <c r="A153" s="4">
         <v>44682</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="6">
+      <c r="A154" s="4">
         <v>44713</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
+      <c r="A155" s="4">
         <v>44743</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
+      <c r="A156" s="4">
         <v>44774</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
+      <c r="A157" s="4">
         <v>44805</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
+      <c r="A158" s="4">
         <v>44835</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
+      <c r="A159" s="4">
         <v>44866</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
+      <c r="A160" s="4">
         <v>44896</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
+      <c r="A161" s="4">
         <v>44927</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="6">
+      <c r="A162" s="4">
         <v>44958</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="6">
+      <c r="A163" s="4">
         <v>44986</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
+      <c r="A164" s="4">
         <v>45017</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="6">
+      <c r="A165" s="4">
         <v>45047</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="6">
+      <c r="A166" s="4">
         <v>45078</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="6">
+      <c r="A167" s="4">
         <v>45108</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="6">
+      <c r="A168" s="4">
         <v>45139</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
+      <c r="A169" s="4">
         <v>45170</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="6">
+      <c r="A170" s="4">
         <v>45200</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="6">
+      <c r="A171" s="4">
         <v>45231</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="6">
+      <c r="A172" s="4">
         <v>45261</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="6">
+      <c r="A173" s="4">
         <v>45292</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="6">
+      <c r="A174" s="4">
         <v>45323</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="6">
+      <c r="A175" s="4">
         <v>45352</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
+      <c r="A176" s="4">
         <v>45383</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
+      <c r="A177" s="4">
         <v>45413</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="6">
+      <c r="A178" s="4">
         <v>45444</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
+      <c r="A179" s="4">
         <v>45474</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="6">
+      <c r="A180" s="4">
         <v>45505</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="6">
+      <c r="A181" s="4">
         <v>45536</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
+      <c r="A182" s="4">
         <v>45566</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+      <c r="A183" s="4">
         <v>45597</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
+      <c r="A184" s="4">
         <v>45627</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
+      <c r="A185" s="4">
         <v>45658</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="6">
+      <c r="A186" s="4">
         <v>45689</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="6">
+      <c r="A187" s="4">
         <v>45717</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="6">
+      <c r="A188" s="4">
         <v>45748</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="6">
+      <c r="A189" s="4">
         <v>45778</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="6">
+      <c r="A190" s="4">
         <v>45809</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="6">
+      <c r="A191" s="4">
         <v>45839</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="6">
+      <c r="A192" s="4">
         <v>45870</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="6">
+      <c r="A193" s="4">
         <v>45901</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="6">
+      <c r="A194" s="4">
         <v>45931</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="6">
+      <c r="A195" s="4">
         <v>45962</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="6">
+      <c r="A196" s="4">
         <v>45992</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="6">
+      <c r="A197" s="4">
         <v>46023</v>
       </c>
     </row>
@@ -8911,102 +8840,102 @@
     </row>
     <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s">
         <v>81</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
         <v>81</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>81</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>56</v>
+      </c>
+      <c r="R3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" t="s">
         <v>82</v>
       </c>
-      <c r="I3" t="s">
+      <c r="T3" t="s">
         <v>82</v>
       </c>
-      <c r="J3" t="s">
+      <c r="U3" t="s">
         <v>82</v>
       </c>
-      <c r="K3" t="s">
+      <c r="V3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W3" t="s">
+        <v>83</v>
+      </c>
+      <c r="X3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL3" t="s">
         <v>56</v>
       </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O3" t="s">
-        <v>57</v>
-      </c>
-      <c r="P3" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R3" t="s">
-        <v>57</v>
-      </c>
-      <c r="S3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U3" t="s">
-        <v>83</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="AP3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS3" t="s">
         <v>84</v>
       </c>
-      <c r="W3" t="s">
-        <v>84</v>
-      </c>
-      <c r="X3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>57</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AS3" t="s">
+      <c r="AW3" t="s">
         <v>85</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
@@ -9041,7 +8970,7 @@
         <v>8</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
         <v>9</v>
@@ -9053,7 +8982,7 @@
         <v>8</v>
       </c>
       <c r="P4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q4" t="s">
         <v>9</v>
@@ -9110,7 +9039,7 @@
         <v>8</v>
       </c>
       <c r="AI4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ4" t="s">
         <v>9</v>
@@ -9122,7 +9051,7 @@
         <v>8</v>
       </c>
       <c r="AM4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AN4" t="s">
         <v>9</v>
@@ -9143,7 +9072,7 @@
         <v>8</v>
       </c>
       <c r="AT4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AU4" t="s">
         <v>9</v>
@@ -9155,7 +9084,7 @@
         <v>8</v>
       </c>
       <c r="AX4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AY4" t="s">
         <v>9</v>
@@ -9165,967 +9094,967 @@
       </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>40179</v>
       </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>40210</v>
       </c>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>40238</v>
       </c>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>40269</v>
       </c>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>40299</v>
       </c>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>40330</v>
       </c>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>40360</v>
       </c>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>40391</v>
       </c>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>40422</v>
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>40452</v>
       </c>
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>40483</v>
       </c>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>40513</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>40544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>40575</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>40603</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>40634</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>40664</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>40695</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>40725</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>40756</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>40787</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="4">
         <v>40817</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>40848</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>40878</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>40909</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="4">
         <v>40940</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="4">
         <v>40969</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="4">
         <v>41000</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="4">
         <v>41030</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="4">
         <v>41061</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>41091</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="4">
         <v>41122</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="4">
         <v>41153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="4">
         <v>41183</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="4">
         <v>41214</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="4">
         <v>41244</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="4">
         <v>41275</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="4">
         <v>41306</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="4">
         <v>41334</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="4">
         <v>41365</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="4">
         <v>41395</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="4">
         <v>41426</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="4">
         <v>41456</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="4">
         <v>41487</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="4">
         <v>41518</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>41548</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="4">
         <v>41579</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="4">
         <v>41609</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="4">
         <v>41640</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="4">
         <v>41671</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="4">
         <v>41699</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="4">
         <v>41730</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="4">
         <v>41760</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="4">
         <v>41791</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="4">
         <v>41821</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
+      <c r="A60" s="4">
         <v>41852</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="A61" s="4">
         <v>41883</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+      <c r="A62" s="4">
         <v>41913</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="A63" s="4">
         <v>41944</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+      <c r="A64" s="4">
         <v>41974</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
+      <c r="A65" s="4">
         <v>42005</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+      <c r="A66" s="4">
         <v>42036</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
+      <c r="A67" s="4">
         <v>42064</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
+      <c r="A68" s="4">
         <v>42095</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="A69" s="4">
         <v>42125</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="A70" s="4">
         <v>42156</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+      <c r="A71" s="4">
         <v>42186</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
+      <c r="A72" s="4">
         <v>42217</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+      <c r="A73" s="4">
         <v>42248</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
+      <c r="A74" s="4">
         <v>42278</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
+      <c r="A75" s="4">
         <v>42309</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
+      <c r="A76" s="4">
         <v>42339</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+      <c r="A77" s="4">
         <v>42370</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+      <c r="A78" s="4">
         <v>42401</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+      <c r="A79" s="4">
         <v>42430</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+      <c r="A80" s="4">
         <v>42461</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="A81" s="4">
         <v>42491</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+      <c r="A82" s="4">
         <v>42522</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+      <c r="A83" s="4">
         <v>42552</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="A84" s="4">
         <v>42583</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="A85" s="4">
         <v>42614</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="A86" s="4">
         <v>42644</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="A87" s="4">
         <v>42675</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="A88" s="4">
         <v>42705</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+      <c r="A89" s="4">
         <v>42736</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+      <c r="A90" s="4">
         <v>42767</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="A91" s="4">
         <v>42795</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="A92" s="4">
         <v>42826</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="A93" s="4">
         <v>42856</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="A94" s="4">
         <v>42887</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="A95" s="4">
         <v>42917</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="A96" s="4">
         <v>42948</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="A97" s="4">
         <v>42979</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="A98" s="4">
         <v>43009</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
+      <c r="A99" s="4">
         <v>43040</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
+      <c r="A100" s="4">
         <v>43070</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
+      <c r="A101" s="4">
         <v>43101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="A102" s="4">
         <v>43132</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="A103" s="4">
         <v>43160</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="A104" s="4">
         <v>43191</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="A105" s="4">
         <v>43221</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="A106" s="4">
         <v>43252</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="A107" s="4">
         <v>43282</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="A108" s="4">
         <v>43313</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="A109" s="4">
         <v>43344</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="A110" s="4">
         <v>43374</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="A111" s="4">
         <v>43405</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="A112" s="4">
         <v>43435</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
+      <c r="A113" s="4">
         <v>43466</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
+      <c r="A114" s="4">
         <v>43497</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
+      <c r="A115" s="4">
         <v>43525</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
+      <c r="A116" s="4">
         <v>43556</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="A117" s="4">
         <v>43586</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
+      <c r="A118" s="4">
         <v>43617</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
+      <c r="A119" s="4">
         <v>43647</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
+      <c r="A120" s="4">
         <v>43678</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
+      <c r="A121" s="4">
         <v>43709</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
+      <c r="A122" s="4">
         <v>43739</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
+      <c r="A123" s="4">
         <v>43770</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="A124" s="4">
         <v>43800</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="A125" s="4">
         <v>43831</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
+      <c r="A126" s="4">
         <v>43862</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
+      <c r="A127" s="4">
         <v>43891</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
+      <c r="A128" s="4">
         <v>43922</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="A129" s="4">
         <v>43952</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
+      <c r="A130" s="4">
         <v>43983</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
+      <c r="A131" s="4">
         <v>44013</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
+      <c r="A132" s="4">
         <v>44044</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="6">
+      <c r="A133" s="4">
         <v>44075</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="6">
+      <c r="A134" s="4">
         <v>44105</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="6">
+      <c r="A135" s="4">
         <v>44136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="6">
+      <c r="A136" s="4">
         <v>44166</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
+      <c r="A137" s="4">
         <v>44197</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="6">
+      <c r="A138" s="4">
         <v>44228</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="6">
+      <c r="A139" s="4">
         <v>44256</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="6">
+      <c r="A140" s="4">
         <v>44287</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="A141" s="4">
         <v>44317</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
+      <c r="A142" s="4">
         <v>44348</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
+      <c r="A143" s="4">
         <v>44378</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="A144" s="4">
         <v>44409</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
+      <c r="A145" s="4">
         <v>44440</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="A146" s="4">
         <v>44470</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
+      <c r="A147" s="4">
         <v>44501</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
+      <c r="A148" s="4">
         <v>44531</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
+      <c r="A149" s="4">
         <v>44562</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
+      <c r="A150" s="4">
         <v>44593</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
+      <c r="A151" s="4">
         <v>44621</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
+      <c r="A152" s="4">
         <v>44652</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
+      <c r="A153" s="4">
         <v>44682</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="6">
+      <c r="A154" s="4">
         <v>44713</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
+      <c r="A155" s="4">
         <v>44743</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
+      <c r="A156" s="4">
         <v>44774</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
+      <c r="A157" s="4">
         <v>44805</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
+      <c r="A158" s="4">
         <v>44835</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
+      <c r="A159" s="4">
         <v>44866</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
+      <c r="A160" s="4">
         <v>44896</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
+      <c r="A161" s="4">
         <v>44927</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="6">
+      <c r="A162" s="4">
         <v>44958</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="6">
+      <c r="A163" s="4">
         <v>44986</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
+      <c r="A164" s="4">
         <v>45017</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="6">
+      <c r="A165" s="4">
         <v>45047</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="6">
+      <c r="A166" s="4">
         <v>45078</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="6">
+      <c r="A167" s="4">
         <v>45108</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="6">
+      <c r="A168" s="4">
         <v>45139</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
+      <c r="A169" s="4">
         <v>45170</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="6">
+      <c r="A170" s="4">
         <v>45200</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="6">
+      <c r="A171" s="4">
         <v>45231</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="6">
+      <c r="A172" s="4">
         <v>45261</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="6">
+      <c r="A173" s="4">
         <v>45292</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="6">
+      <c r="A174" s="4">
         <v>45323</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="6">
+      <c r="A175" s="4">
         <v>45352</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
+      <c r="A176" s="4">
         <v>45383</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
+      <c r="A177" s="4">
         <v>45413</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="6">
+      <c r="A178" s="4">
         <v>45444</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
+      <c r="A179" s="4">
         <v>45474</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="6">
+      <c r="A180" s="4">
         <v>45505</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="6">
+      <c r="A181" s="4">
         <v>45536</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
+      <c r="A182" s="4">
         <v>45566</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+      <c r="A183" s="4">
         <v>45597</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
+      <c r="A184" s="4">
         <v>45627</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
+      <c r="A185" s="4">
         <v>45658</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="6">
+      <c r="A186" s="4">
         <v>45689</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="6">
+      <c r="A187" s="4">
         <v>45717</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="6">
+      <c r="A188" s="4">
         <v>45748</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="6">
+      <c r="A189" s="4">
         <v>45778</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="6">
+      <c r="A190" s="4">
         <v>45809</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="6">
+      <c r="A191" s="4">
         <v>45839</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="6">
+      <c r="A192" s="4">
         <v>45870</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="6">
+      <c r="A193" s="4">
         <v>45901</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="6">
+      <c r="A194" s="4">
         <v>45931</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="6">
+      <c r="A195" s="4">
         <v>45962</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="6">
+      <c r="A196" s="4">
         <v>45992</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="6">
+      <c r="A197" s="4">
         <v>46023</v>
       </c>
     </row>
@@ -10146,102 +10075,102 @@
     </row>
     <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s">
         <v>81</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
         <v>81</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>81</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>56</v>
+      </c>
+      <c r="R3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" t="s">
         <v>82</v>
       </c>
-      <c r="I3" t="s">
+      <c r="T3" t="s">
         <v>82</v>
       </c>
-      <c r="J3" t="s">
+      <c r="U3" t="s">
         <v>82</v>
       </c>
-      <c r="K3" t="s">
+      <c r="V3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W3" t="s">
+        <v>83</v>
+      </c>
+      <c r="X3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL3" t="s">
         <v>56</v>
       </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O3" t="s">
-        <v>57</v>
-      </c>
-      <c r="P3" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R3" t="s">
-        <v>57</v>
-      </c>
-      <c r="S3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U3" t="s">
-        <v>83</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="AP3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS3" t="s">
         <v>84</v>
       </c>
-      <c r="W3" t="s">
-        <v>84</v>
-      </c>
-      <c r="X3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>57</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AS3" t="s">
+      <c r="AW3" t="s">
         <v>85</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
@@ -10276,7 +10205,7 @@
         <v>8</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
         <v>9</v>
@@ -10288,7 +10217,7 @@
         <v>8</v>
       </c>
       <c r="P4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q4" t="s">
         <v>9</v>
@@ -10345,7 +10274,7 @@
         <v>8</v>
       </c>
       <c r="AI4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ4" t="s">
         <v>9</v>
@@ -10357,7 +10286,7 @@
         <v>8</v>
       </c>
       <c r="AM4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AN4" t="s">
         <v>9</v>
@@ -10378,7 +10307,7 @@
         <v>8</v>
       </c>
       <c r="AT4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AU4" t="s">
         <v>9</v>
@@ -10390,7 +10319,7 @@
         <v>8</v>
       </c>
       <c r="AX4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AY4" t="s">
         <v>9</v>
@@ -10400,967 +10329,967 @@
       </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>40179</v>
       </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>40210</v>
       </c>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>40238</v>
       </c>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>40269</v>
       </c>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>40299</v>
       </c>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>40330</v>
       </c>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>40360</v>
       </c>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>40391</v>
       </c>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>40422</v>
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>40452</v>
       </c>
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>40483</v>
       </c>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>40513</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>40544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>40575</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>40603</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>40634</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>40664</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>40695</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>40725</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>40756</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>40787</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="4">
         <v>40817</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>40848</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>40878</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="4">
         <v>40909</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="4">
         <v>40940</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="4">
         <v>40969</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="4">
         <v>41000</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="4">
         <v>41030</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="4">
         <v>41061</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>41091</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="4">
         <v>41122</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="4">
         <v>41153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="4">
         <v>41183</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="4">
         <v>41214</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="4">
         <v>41244</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="4">
         <v>41275</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="4">
         <v>41306</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="4">
         <v>41334</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="4">
         <v>41365</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="4">
         <v>41395</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="4">
         <v>41426</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="4">
         <v>41456</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="4">
         <v>41487</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="4">
         <v>41518</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>41548</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="4">
         <v>41579</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="4">
         <v>41609</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="4">
         <v>41640</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="4">
         <v>41671</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="4">
         <v>41699</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="4">
         <v>41730</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="4">
         <v>41760</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="4">
         <v>41791</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="4">
         <v>41821</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
+      <c r="A60" s="4">
         <v>41852</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="A61" s="4">
         <v>41883</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+      <c r="A62" s="4">
         <v>41913</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="A63" s="4">
         <v>41944</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+      <c r="A64" s="4">
         <v>41974</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
+      <c r="A65" s="4">
         <v>42005</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+      <c r="A66" s="4">
         <v>42036</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
+      <c r="A67" s="4">
         <v>42064</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
+      <c r="A68" s="4">
         <v>42095</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="A69" s="4">
         <v>42125</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="A70" s="4">
         <v>42156</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+      <c r="A71" s="4">
         <v>42186</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
+      <c r="A72" s="4">
         <v>42217</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+      <c r="A73" s="4">
         <v>42248</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
+      <c r="A74" s="4">
         <v>42278</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
+      <c r="A75" s="4">
         <v>42309</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
+      <c r="A76" s="4">
         <v>42339</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+      <c r="A77" s="4">
         <v>42370</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+      <c r="A78" s="4">
         <v>42401</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+      <c r="A79" s="4">
         <v>42430</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+      <c r="A80" s="4">
         <v>42461</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="A81" s="4">
         <v>42491</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+      <c r="A82" s="4">
         <v>42522</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+      <c r="A83" s="4">
         <v>42552</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="A84" s="4">
         <v>42583</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="A85" s="4">
         <v>42614</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="A86" s="4">
         <v>42644</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="A87" s="4">
         <v>42675</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="A88" s="4">
         <v>42705</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+      <c r="A89" s="4">
         <v>42736</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+      <c r="A90" s="4">
         <v>42767</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="A91" s="4">
         <v>42795</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="A92" s="4">
         <v>42826</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="A93" s="4">
         <v>42856</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="A94" s="4">
         <v>42887</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="A95" s="4">
         <v>42917</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="A96" s="4">
         <v>42948</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="A97" s="4">
         <v>42979</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="A98" s="4">
         <v>43009</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
+      <c r="A99" s="4">
         <v>43040</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
+      <c r="A100" s="4">
         <v>43070</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
+      <c r="A101" s="4">
         <v>43101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="A102" s="4">
         <v>43132</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="A103" s="4">
         <v>43160</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="A104" s="4">
         <v>43191</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="A105" s="4">
         <v>43221</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="A106" s="4">
         <v>43252</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="A107" s="4">
         <v>43282</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="A108" s="4">
         <v>43313</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="A109" s="4">
         <v>43344</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="A110" s="4">
         <v>43374</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="A111" s="4">
         <v>43405</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="A112" s="4">
         <v>43435</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
+      <c r="A113" s="4">
         <v>43466</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
+      <c r="A114" s="4">
         <v>43497</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
+      <c r="A115" s="4">
         <v>43525</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
+      <c r="A116" s="4">
         <v>43556</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="A117" s="4">
         <v>43586</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
+      <c r="A118" s="4">
         <v>43617</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
+      <c r="A119" s="4">
         <v>43647</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
+      <c r="A120" s="4">
         <v>43678</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
+      <c r="A121" s="4">
         <v>43709</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
+      <c r="A122" s="4">
         <v>43739</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
+      <c r="A123" s="4">
         <v>43770</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="A124" s="4">
         <v>43800</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="A125" s="4">
         <v>43831</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
+      <c r="A126" s="4">
         <v>43862</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
+      <c r="A127" s="4">
         <v>43891</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
+      <c r="A128" s="4">
         <v>43922</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="A129" s="4">
         <v>43952</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
+      <c r="A130" s="4">
         <v>43983</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
+      <c r="A131" s="4">
         <v>44013</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
+      <c r="A132" s="4">
         <v>44044</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="6">
+      <c r="A133" s="4">
         <v>44075</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="6">
+      <c r="A134" s="4">
         <v>44105</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="6">
+      <c r="A135" s="4">
         <v>44136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="6">
+      <c r="A136" s="4">
         <v>44166</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
+      <c r="A137" s="4">
         <v>44197</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="6">
+      <c r="A138" s="4">
         <v>44228</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="6">
+      <c r="A139" s="4">
         <v>44256</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="6">
+      <c r="A140" s="4">
         <v>44287</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="A141" s="4">
         <v>44317</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
+      <c r="A142" s="4">
         <v>44348</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
+      <c r="A143" s="4">
         <v>44378</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="A144" s="4">
         <v>44409</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
+      <c r="A145" s="4">
         <v>44440</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="A146" s="4">
         <v>44470</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
+      <c r="A147" s="4">
         <v>44501</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
+      <c r="A148" s="4">
         <v>44531</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
+      <c r="A149" s="4">
         <v>44562</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
+      <c r="A150" s="4">
         <v>44593</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
+      <c r="A151" s="4">
         <v>44621</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
+      <c r="A152" s="4">
         <v>44652</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
+      <c r="A153" s="4">
         <v>44682</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="6">
+      <c r="A154" s="4">
         <v>44713</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
+      <c r="A155" s="4">
         <v>44743</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
+      <c r="A156" s="4">
         <v>44774</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
+      <c r="A157" s="4">
         <v>44805</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
+      <c r="A158" s="4">
         <v>44835</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
+      <c r="A159" s="4">
         <v>44866</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
+      <c r="A160" s="4">
         <v>44896</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
+      <c r="A161" s="4">
         <v>44927</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="6">
+      <c r="A162" s="4">
         <v>44958</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="6">
+      <c r="A163" s="4">
         <v>44986</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
+      <c r="A164" s="4">
         <v>45017</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="6">
+      <c r="A165" s="4">
         <v>45047</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="6">
+      <c r="A166" s="4">
         <v>45078</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="6">
+      <c r="A167" s="4">
         <v>45108</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="6">
+      <c r="A168" s="4">
         <v>45139</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
+      <c r="A169" s="4">
         <v>45170</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="6">
+      <c r="A170" s="4">
         <v>45200</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="6">
+      <c r="A171" s="4">
         <v>45231</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="6">
+      <c r="A172" s="4">
         <v>45261</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="6">
+      <c r="A173" s="4">
         <v>45292</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="6">
+      <c r="A174" s="4">
         <v>45323</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="6">
+      <c r="A175" s="4">
         <v>45352</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
+      <c r="A176" s="4">
         <v>45383</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
+      <c r="A177" s="4">
         <v>45413</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="6">
+      <c r="A178" s="4">
         <v>45444</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
+      <c r="A179" s="4">
         <v>45474</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="6">
+      <c r="A180" s="4">
         <v>45505</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="6">
+      <c r="A181" s="4">
         <v>45536</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
+      <c r="A182" s="4">
         <v>45566</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+      <c r="A183" s="4">
         <v>45597</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
+      <c r="A184" s="4">
         <v>45627</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
+      <c r="A185" s="4">
         <v>45658</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="6">
+      <c r="A186" s="4">
         <v>45689</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="6">
+      <c r="A187" s="4">
         <v>45717</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="6">
+      <c r="A188" s="4">
         <v>45748</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="6">
+      <c r="A189" s="4">
         <v>45778</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="6">
+      <c r="A190" s="4">
         <v>45809</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="6">
+      <c r="A191" s="4">
         <v>45839</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="6">
+      <c r="A192" s="4">
         <v>45870</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="6">
+      <c r="A193" s="4">
         <v>45901</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="6">
+      <c r="A194" s="4">
         <v>45931</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="6">
+      <c r="A195" s="4">
         <v>45962</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="6">
+      <c r="A196" s="4">
         <v>45992</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="6">
+      <c r="A197" s="4">
         <v>46023</v>
       </c>
     </row>
